--- a/resultados/toledo/inventario_externos.xlsx
+++ b/resultados/toledo/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2109"/>
+  <dimension ref="A1:G2309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72909,6 +72909,6970 @@
         </is>
       </c>
     </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>https://www.aen.pr.gov.br/sites/default/arquivos_restritos/files/documento/2024-05/0105oficioms.pdf</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>Ofício Circular nº 142/2024/SVSA/MS</t>
+        </is>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/doses-de-vacina-contra-dengue-comecam-ser-aplicadas-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2110" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2110" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/saude/pt-br/centrais-de-conteudo/publicacoes/notas-tecnicas/2024/nota-tecnica-no-47-2024-cgirf-dpni-svsa-ms</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>www.gov.br</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>Nota Técnica nº 47/2024</t>
+        </is>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/boletim-semanal-aponta-para-4251-casos-e-19-obitos-por-dengue-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2111" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2111" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:41:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send/?phone=5545991336391</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>(45) 99133-6391 (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/calor-intenso-coloca-toledo-em-estado-de-alerta-em-relacao-ao-aedes-aegypti</t>
+        </is>
+      </c>
+      <c r="F2112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2112" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:42:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/live/9tok026kZpI?si=JmIl1iZkPxttqoCV</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>durante o pequeno expediente da sessão ordinária ocorrida na tarde desta segunda</t>
+        </is>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/gabinete/gabinete-do-prefeito-recebe-futura-diretora-geral-do-campus-toledo-da-ufpr</t>
+        </is>
+      </c>
+      <c r="F2113" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2113" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:44:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>https://br.linkedin.com/company/ideas-sa%C3%BAde</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>br.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>Instituto de Desenvolvimento, Ensino e Assistência à Saúde</t>
+        </is>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/estruturas-de-saude-de-toledo-sao-visitadas-por-avaliadores-do-mec</t>
+        </is>
+      </c>
+      <c r="F2114" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2114" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:44:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>https://www.documentador.pr.gov.br/documentador/pub.do?action=d&amp;uuid=@gtf-escriba-sesa@51b5787c-780d-4d00-bed0-b2c8e66c5c35</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>www.documentador.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>Resolução nº 924/2024</t>
+        </is>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/caps-de-toledo-passam-oferecer-oficinas-terapeuticas-de-artesanato</t>
+        </is>
+      </c>
+      <c r="F2115" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2115" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:44:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ondafurtacor.toledopr/</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>@ondafurtacor.toledopr</t>
+        </is>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/maio-furta-cor-toledo-realiza-atividades-focadas-na-saude-mental-materna</t>
+        </is>
+      </c>
+      <c r="F2116" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2116" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:44:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>https://bvsms.saude.gov.br/bvs/saudelegis/gm/2002/prt0336_19_02_2002.html</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>bvsms.saude.gov.br</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>nº 336/2002</t>
+        </is>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/adolescentes-atendidos-pelo-capsi-fazem-visita-guiada-ao-zoo-de-cascavel</t>
+        </is>
+      </c>
+      <c r="F2117" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2117" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:44:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>https://bvsms.saude.gov.br/bvs/saudelegis/gm/2011/prt3088_23_12_2011_rep.html</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>bvsms.saude.gov.br</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>nº 3.088/2011</t>
+        </is>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/adolescentes-atendidos-pelo-capsi-fazem-visita-guiada-ao-zoo-de-cascavel</t>
+        </is>
+      </c>
+      <c r="F2118" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2118" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:44:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLScQQcfY5KW19qGxeShYSRc3Qf0f2bNSAog042WuPQQSWEK98Q/viewform?pli=1</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr"/>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/setembro-amarelo-2025-movimento-pela-vida-esta-com-inscricoes-abertas</t>
+        </is>
+      </c>
+      <c r="F2119" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2119" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:45:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>https://www.unipar.br/eventos/6195/setembro-amarelo-2025-movimento-pela-vida/</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>www.unipar.br</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>https://www.unipar.br/eventos/6195/setembro-amarelo-2025-movimento-pela-vida/</t>
+        </is>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/setembro-amarelo-2025-movimento-pela-vida-esta-com-inscricoes-abertas</t>
+        </is>
+      </c>
+      <c r="F2120" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2120" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:45:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1u1oc6qwxi2OBTcXEMDdckVmxoyRXYAfkN4N3QUokW98/edit</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1u1oc6qwxi2OBTcXEMDdckVmxoyRXYAfkN4N3QUokW98/edit</t>
+        </is>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/saude-estara-em-capacitacao-na-camara-sobre-manobra-de-heimlich</t>
+        </is>
+      </c>
+      <c r="F2121" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2121" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>https://www.unipar.br/eventos/toledo/</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>www.unipar.br</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>www.unipar.br/eventos/toledo</t>
+        </is>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/saude-mental-define-programacao-de-eventos-alusivos-ao-setembro-amarelo</t>
+        </is>
+      </c>
+      <c r="F2122" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2122" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:45:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>https://encurtador.com.br/fkoz7</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>encurtador.com.br</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>https://encurtador.com.br/fkoz7</t>
+        </is>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/secretaria-de-saude-tera-diversas-acoes-alusiva-ao-setembro-amarelo</t>
+        </is>
+      </c>
+      <c r="F2123" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2123" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:48:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>https://encurtador.com.br/gjtvQ</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>encurtador.com.br</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>https://encurtador.com.br/gjtvQ</t>
+        </is>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/secretaria-de-saude-tera-diversas-acoes-alusiva-ao-setembro-amarelo</t>
+        </is>
+      </c>
+      <c r="F2124" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2124" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:48:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/Revolu%C3%A7%C3%A3o_de_1923</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>Revolução de 1923</t>
+        </is>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/semana-farroupilha-consolida-toledo-como-referencia-da-cultura-tradicionalista</t>
+        </is>
+      </c>
+      <c r="F2125" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2125" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:50:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSe60gOT-wKcSHqpGpRAej26tWlL0YCKC3UxmV5fYgdd4gh6Ag/viewform?pli=1</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/desenvolvimento-economico-e-turismo/deseco-promove-evento-sobre-alteracao-na-nr-1-e-seus</t>
+        </is>
+      </c>
+      <c r="F2126" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2126" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:50:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1CWCdOzsPyQqdRFyyQ6g7mPynKDTTuZYZ/edit</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>disponíveis clicando aqui.</t>
+        </is>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/educacao/smed-realiza-o-primeiro-campeonato-de-robotica-educacional-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2127" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2127" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:55:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MWiaOlKKy0wMgPm6TuErtwwA9FlOKxr5/view</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>lista completa</t>
+        </is>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/educacao/smed-realiza-chamamento-de-165-criancas-que-aguardavam-vagas-em-cmeis</t>
+        </is>
+      </c>
+      <c r="F2128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2128" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:56:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Wv8AIOprWouvWBTg8elOSTSSiXDgexvC/view</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>lista completa</t>
+        </is>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/educacao/smed-faz-chamamento-de-200-criancas-que-aguardavam-vaga-em-cmeis</t>
+        </is>
+      </c>
+      <c r="F2129" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2129" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:56:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1BSqRET6QxOQTkS1HtlbYyxoSJZ-8aftE/view</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>confira a lista clicando aqui</t>
+        </is>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/educacao/educacao-chamou-mais-345-criancas-para-ingressar-na-educacao-infantil</t>
+        </is>
+      </c>
+      <c r="F2130" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2130" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:56:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>https://www.esporte.pr.gov.br/JEPS/webservices/documentador/Documentos-Oficiais-JEPs-Fase-Estadual</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>www.esporte.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/esportes-e-lazer/toledo-se-destaca-no-judo-e-no-taekwondo-nos-71o-jogos-escolares-do</t>
+        </is>
+      </c>
+      <c r="F2131" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2131" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSe7iHpiItu38if-HbSyhQ0GwyU3tgEuvlQTd6ufRr8t7IYH_g/viewform</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>formulário on-line</t>
+        </is>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/esportes-e-lazer/estao-abertas-inscricoes-para-os-jogos-da-semana-da-mulher</t>
+        </is>
+      </c>
+      <c r="F2132" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2132" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:57:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSeZU2SE2ijiBDr9SJnRshP_0PeRxckl4LFj_lpyOIQ5VqOvmg/viewform</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>formulário do circuito</t>
+        </is>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/esportes-e-lazer/circuito-municipal-de-volei-de-praia-abre-temporada-do-esporte-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2133" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2133" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:57:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ekpJKuZChLI</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>canal da Câmara de Toledo</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/esportes-e-lazer/smel-faz-prestacao-de-contas-do-terceiro-quadrimestre-de-2023</t>
+        </is>
+      </c>
+      <c r="F2134" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2134" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:57:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>http://www.basqueteparana.com.br</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>www.basqueteparana.com.br</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>www.basqueteparana.com.br</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/esportes-e-lazer/toledo-recebe-campeonato-paranaense-de-basquete-serie-prata</t>
+        </is>
+      </c>
+      <c r="F2135" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2135" t="inlineStr">
+        <is>
+          <t>2026-08-23 23:57:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>https://www.meiamaratonadetoledo.com.br/</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>www.meiamaratonadetoledo.com.br</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>site da prova</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/esportes-e-lazer/cerimonia-marca-abertura-da-24a-meia-maratona-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2136" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2136" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:04:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>https://www.in.gov.br/web/dou/-/portaria-gm/ms-n-5.508-de-24-de-outubro-de-2024-592799868</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>www.in.gov.br</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>Portaria GM/MS nº 5.508, de 24 de outubro de 2024</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/toledo-tem-mais-8-esb-e-5-esf-credenciadas-pelo-ministerio-da-saude</t>
+        </is>
+      </c>
+      <c r="F2137" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2137" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:04:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>https://www.in.gov.br/web/dou/-/portaria-gm/ms-n-5.610-de-23-de-outubro-de-2024-592472056</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>www.in.gov.br</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>Portaria GM/MS nº 5.610, de 23 de outubro de 2024</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/toledo-tem-mais-8-esb-e-5-esf-credenciadas-pelo-ministerio-da-saude</t>
+        </is>
+      </c>
+      <c r="F2138" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2138" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:04:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iLm3EijDTak</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>canal da Casa no YouTube</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/saude-toledo-destina-3243-das-receitas-o-dobro-do-minimo-constitucional</t>
+        </is>
+      </c>
+      <c r="F2139" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2139" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/live/WnU5Flej5M8?si=uD0Wgc9aWBDB2NeA</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/relatorio-de-atividades-e-apresentado-pela-cultura-em-audiencia-publica-na-camara</t>
+        </is>
+      </c>
+      <c r="F2140" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2140" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PuNRJ1Idwd0</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>primeira sessão ordinária da Câmara de Vereadores em 2024</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/gabinete/executivo-marca-presenca-em-abertura-dos-trabalhos-da-camara-em-2024</t>
+        </is>
+      </c>
+      <c r="F2141" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2141" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:05:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BFTjmpMZO2U?si=05ypw5rQZhJt45Nr&amp;t=7</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>Hino da Diocese de Toledo</t>
+        </is>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/exposicao-no-museu-willy-barth-exalta-o-papel-da-igreja-na-historia-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2142" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2142" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:06:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>https://festivaldascataratas.com/</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>festivaldascataratas.com</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>18º Festival das Cataratas</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/gabinete/comitiva-representa-toledo-em-evento-sobre-turismo-em-foz-do-iguacu</t>
+        </is>
+      </c>
+      <c r="F2143" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2143" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:06:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/turismo/pt-br/assuntos/noticias/no-festival-das-cataratas-em-foz-do-iguacu-pr-ministra-daniela-carneiro-defende-uniao-de-paises-do-mercosul-para-fortalecer-o-turismo-nas-fronteiras</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>www.gov.br</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>defendeu a união de países do Mercosul para fortalecer o turismo nas fronteiras</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/gabinete/comitiva-representa-toledo-em-evento-sobre-turismo-em-foz-do-iguacu</t>
+        </is>
+      </c>
+      <c r="F2144" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2144" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:06:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfGw35Fx57Is_acYpgbgaPSo1WrtXPSpogFK0fGU266shOXsQ/viewform</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>inscrição neste link</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/desenvolvimento-economico-e-turismo/feira-do-empreendedor-prefeitura-disponibiliza-vagas</t>
+        </is>
+      </c>
+      <c r="F2145" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2145" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:06:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>https://www.documentador.pr.gov.br/documentador/pub.do?action=d&amp;uuid=@gtf-escriba-sesa@1219ef0c-f7ac-43aa-8975-09e1d4c73a62</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>www.documentador.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>Resolução nº 870/2021</t>
+        </is>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/centro-especializado-em-reabilitacao-recebe-recursos-do-governo-do-parana</t>
+        </is>
+      </c>
+      <c r="F2146" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2146" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:06:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSd4sNKbdtWbsCH3lV-pGMH6mYcl7bvaV9Kqm9v-HgE0BJbHrg/viewform?fbzx=5745177486678423924</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>formulário online</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/inscricoes-para-49deg-festival-de-inverno-festin-estao-abertas</t>
+        </is>
+      </c>
+      <c r="F2147" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2147" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ZUeTtqSTvj1QuuFT7</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ZUeTtqSTvj1QuuFT7</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/cultura-divulga-regulamento-e-abre-inscricoes-para-o-48o-festin</t>
+        </is>
+      </c>
+      <c r="F2148" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2148" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>https://forms.gle/tGespBb5LRYpUf2JA</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>https://forms.gle/tGespBb5LRYpUf2JA</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/cultura-encerra-sexta-26-inscricoes-para-festivais-de-danca-e-de-musica-gospel</t>
+        </is>
+      </c>
+      <c r="F2149" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2149" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>https://forms.gle/sWDbUZfgVg7GjjnQ6</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>inscrições</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/cultura-encerra-sexta-26-inscricoes-para-festivais-de-danca-e-de-musica-gospel</t>
+        </is>
+      </c>
+      <c r="F2150" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2150" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>https://forms.gle/eu4mKZSeH15wUm1G8</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>https://forms.gle/eu4mKZSeH15wUm1G8</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/cultura-encerra-sexta-26-inscricoes-para-festivais-de-danca-e-de-musica-gospel</t>
+        </is>
+      </c>
+      <c r="F2151" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2151" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gxubG8_hPfs</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gxubG8_hPfs</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/artista-de-toledo-integra-equipe-de-producao-artistica-internacional</t>
+        </is>
+      </c>
+      <c r="F2152" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2152" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>https://fb.watch/m7Lrg-0WHj/</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>fb.watch</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>O evento também foi transmitido ao vivo pelas redes sociais da Secretaria de Cultura</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/secretaria-da-cultura-premiou-campeoes-e-campeas-do-festin-no-sabado</t>
+        </is>
+      </c>
+      <c r="F2153" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2153" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLScksD_48i78ExF4yB4s4dNVbSBqc3zeKS8ztgdbNKVSpJ7nlA/closedform</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>As inscrições são gratuitas</t>
+        </is>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/desenvolvimento-economico-e-turismo/concurso-de-decoracao-natalina-de-toledo-de-2024</t>
+        </is>
+      </c>
+      <c r="F2154" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2154" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>http://web.whatsapp.com/send?phone=55%2845%29+99145-4058</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>web.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/job-sala-do-empreendedor-de-toledo-tera-assistente-virtual-dedicado-a-meis</t>
+        </is>
+      </c>
+      <c r="F2155" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2155" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:08:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>http://bit.ly/showsdeaniversariotoledo</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>bit.ly/showsdeaniversariotoledo</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/desenvolvimento-economico-e-turismo/toledo-abre-chamamento-publico-de-shows-locais-para</t>
+        </is>
+      </c>
+      <c r="F2156" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2156" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:09:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DFvu6nHvKbX/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>no Instagram</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/toledo-tem-o-3o-maior-indice-de-acesso-ao-atendimento-pre-natal-do-brasil</t>
+        </is>
+      </c>
+      <c r="F2157" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2157" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfmT3sFRiDxDzlxZXMAHdbOBPC_RJhmclWUEBjL2P7EcBDZ0A/viewform?usp=dialog</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>Projeto Florescer</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/index.php/secretarias/secretaria-da-mulher</t>
+        </is>
+      </c>
+      <c r="F2158" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2158" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:47:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>https://www.planalto.gov.br/ccivil_03/_ato2015-2018/2017/lei/l13465.htm</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>Lei Federal nº 13.465/2017</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/gabinete/regularizacao-de-areas-concedidas-igreja-e-tema-de-encontro-no-paco</t>
+        </is>
+      </c>
+      <c r="F2159" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2159" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:24:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>http://www.igma.aquila.com.br</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>www.igma.aquila.com.br</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>www.igma.aquila.com.br</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/gabinete/toledo-fica-entre-tres-melhores-gestoes-municipais-do-brasil</t>
+        </is>
+      </c>
+      <c r="F2160" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2160" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:30:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>https://www.in.gov.br/web/dou/-/portaria-minc-n-45-de-14-de-julho-de-2023-496689593</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>www.in.gov.br</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>Portaria nº 045/2023</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/agentes-culturais-participam-de-conferencia-intermunicipal-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2161" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2161" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>https://forms.gle/mtWj88spf1HMXWVEA</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>https://forms.gle/mtWj88spf1HMXWVEA</t>
+        </is>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/toledo-recebe-segunda-etapa-da-3a-conferencia-intermunicipal-de-cultura</t>
+        </is>
+      </c>
+      <c r="F2162" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2162" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>http://bit.ly/extencao-unioeste</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>http://bit.ly/extencao-unioeste</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/biblioteca-publica-e-unioeste-promovem-palestras-sobre-literatura-e-filosofia</t>
+        </is>
+      </c>
+      <c r="F2163" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2163" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>https://forms.gle/i17XJZh5wEDavzPa6</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>https://forms.gle/i17XJZh5wEDavzPa6</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/toledo-promove-no-dia-18-6a-edicao-da-conferencia-municipal-de-cultura</t>
+        </is>
+      </c>
+      <c r="F2164" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2164" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>https://festival-intimus.art/galeria/cama-de-rosas-e-espinhos</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>festival-intimus.art</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>“Cama de Rosas e Espinhos”</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/trabalho-de-artistas-de-toledo-tem-qualidade-reconhecida-em-nivel-nacional</t>
+        </is>
+      </c>
+      <c r="F2165" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2165" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/larissasalgadoarte</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>redes sociais</t>
+        </is>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/trabalho-de-artistas-de-toledo-tem-qualidade-reconhecida-em-nivel-nacional</t>
+        </is>
+      </c>
+      <c r="F2166" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2166" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>https://festival-intimus.art/galeria-de-arte/</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>festival-intimus.art</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>https://festival-intimus.art/galeria-de-arte/</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/trabalho-de-artistas-de-toledo-tem-qualidade-reconhecida-em-nivel-nacional</t>
+        </is>
+      </c>
+      <c r="F2167" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2167" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>https://forms.gle/CDMYQJGWQGNz2x7v5</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>https://forms.gle/CDMYQJGWQGNz2x7v5</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/com-regulamento-divulgado-2o-fesfat-inicia-inscricoes-nesta-segunda-10</t>
+        </is>
+      </c>
+      <c r="F2168" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2168" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:31:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vkW-OqwcYTw</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>transmitido ao vivo pelas redes sociais da Prefeitura de Toledo</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/vencedores-do-46o-festival-de-inverno-de-toledo-festin-sao-conhecidos</t>
+        </is>
+      </c>
+      <c r="F2169" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2169" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:32:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PrefeituraMunicipalToledo/videos/552120703213864/?__cft__[0]=AZVYZfxuQabREgz-FgIwdhFgZOHCj9RItv7xz50pW6ewfZEz35hHnU-nzkfc_hUTe1GMGICnTFzlKvq6olvBk29p-zWwZtUgKXzKkHWQ_ngW9GeJkGFn2zGUI35qpbkcdStVNVeT4HkDDU4WviMCaSiOWIK25LyNAAFVzzFWeQtGaQ&amp;__tn__=-UK-R</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>redes sociais da Secretaria da Cultura</t>
+        </is>
+      </c>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/13o-festival-da-musica-gospel-de-toledo-entrega-premiacao-aos-vencedores</t>
+        </is>
+      </c>
+      <c r="F2170" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2170" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:32:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>https://www.diskingressos.com.br/evento/2967/12-06-2022/pr/toledo/os-melhores-do-mundo-hermanoteu-na-terra-de-godah</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>www.diskingressos.com.br</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>entradas</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/contos-e-desencantos-da-inicio-ao-festival-de-teatro-de-toledo-2022</t>
+        </is>
+      </c>
+      <c r="F2171" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2171" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:32:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/B%C3%ADblia</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>Bíblia</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/contos-e-desencantos-da-inicio-ao-festival-de-teatro-de-toledo-2022</t>
+        </is>
+      </c>
+      <c r="F2172" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2172" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:32:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ujqkvmQxU4Vpjr5b9</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>goo.gl</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>Avenida Parigot de Souza, 2946</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/sede-provisoria-da-biblioteca-publica-municipal-abre-as-portas-para-o-publico</t>
+        </is>
+      </c>
+      <c r="F2173" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2173" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:32:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/leis/2003/l10.741.htm</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>Estatuto do Idoso</t>
+        </is>
+      </c>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/idade-plena-toledo-lanca-campanha-que-destina-parte-do-ir-para-o-fmdi</t>
+        </is>
+      </c>
+      <c r="F2174" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2174" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:54:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>https://forms.gle/AjaoenHbnP72JXXM8</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>https://forms.gle/AjaoenHbnP72JXXM8</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/mulher-empreendedora-da-inicio-a-acao-de-smdh-e-agrodesenvolvimento</t>
+        </is>
+      </c>
+      <c r="F2175" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2175" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:00:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>https://forms.gle/NwoS6MuAWkYT2z4U9</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>clicando neste link</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/educacao/estudantes-devem-realizar-pre-cadastro-para-uso-do-transporte-escolar-publico</t>
+        </is>
+      </c>
+      <c r="F2176" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2176" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>https://forms.gle/WGWjhrE4royf6n4z5</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>https://forms.gle/WGWjhrE4royf6n4z5</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/cultura/cultura-e-clube-de-poesia-de-toledo-promovem-oficinas-de-escrita-criativa</t>
+        </is>
+      </c>
+      <c r="F2177" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2177" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/C4gmIb4v3fF/?igsh=dG12enJ1d2lxMHM=</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>O anúncio foi feito pelo prefeito Beto Lunitti e a secretária de Saúde Gabriela Kucharski em um vídeo nas redes sociais oficiais da Prefeitura de Toledo.</t>
+        </is>
+      </c>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/noticias/saude/unidade-sentinela-abrira-aos-sabados-e-tres-ubss-terao-horario-estendido</t>
+        </is>
+      </c>
+      <c r="F2178" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2178" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/13EsW76U2RWPQTZ3VRtI1OHrJw4-CSLNe?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr"/>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2179" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2179" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1UdJNKOacHEbSxcy0iUZNquhGpowzJpDs?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr"/>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2180" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2180" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/126f2vHKJI3L22kzgQEZ4b9hySUCccFCE?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr"/>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2181" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2181" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1nU4oZ-4plv3n8ZFogBDUpUYncnW71LW7?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr"/>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2182" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2182" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1GwOyiP1eT2d0iJ0vVyFTs_LwlnDR5gMR?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr"/>
+      <c r="E2183" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2183" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2183" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1qvSGuUPfXOts6xjsV-UFMSN_nJAURncp?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr"/>
+      <c r="E2184" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2184" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2184" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1wtNUAoUuaCYzAE_ufukN-g3Fm76cwDPc?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr"/>
+      <c r="E2185" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2185" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2185" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@TVMPT/videos</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>TVMPT</t>
+        </is>
+      </c>
+      <c r="E2186" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/geografia</t>
+        </is>
+      </c>
+      <c r="F2186" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2186" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Yh2kp37YsjYhb2fs6</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Yh2kp37YsjYhb2fs6</t>
+        </is>
+      </c>
+      <c r="E2187" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/smas-organiza-seminario-para-celebrar-27-anos-da-loas-e-17-anos-do-suas</t>
+        </is>
+      </c>
+      <c r="F2187" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2187" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:12:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>https://server2.midas.unioeste.br/sgev/eventos/Encontro%20_socioeducacao</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>server2.midas.unioeste.br</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>https://server2.midas.unioeste.br/sgev/eventos/Encontro%20_socioeducacao</t>
+        </is>
+      </c>
+      <c r="E2188" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/cmdca-organiza-vi-encontro-municipal-da-socioeducacao</t>
+        </is>
+      </c>
+      <c r="F2188" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2188" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:13:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>https://alistamento.eb.mil.br/lista-servicos</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>alistamento.eb.mil.br</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>www.alistamento.eb.mil.br</t>
+        </is>
+      </c>
+      <c r="E2189" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/inspecoes-de-saude-para-o-servico-militar-serao-realizadas-no-cju-europa</t>
+        </is>
+      </c>
+      <c r="F2189" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2189" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.leg.br/sessoes-plenarias/audiencias-publicas-1/2022/educacao/2o-quadrimestre-de-2022/apresentacao-da-prestacao-de-contas/view</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>www.toledo.pr.leg.br</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>prestação de contas</t>
+        </is>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/toledo-investiu-r-1051-milhoes-em-educacao-nos-8-primeiros-meses-de-2022</t>
+        </is>
+      </c>
+      <c r="F2190" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2190" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j8iyVt2m0fg</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>transmitida pelo canal da Câmara de Toledo no YouTube</t>
+        </is>
+      </c>
+      <c r="E2191" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/toledo-investiu-r-1051-milhoes-em-educacao-nos-8-primeiros-meses-de-2022</t>
+        </is>
+      </c>
+      <c r="F2191" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2191" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R-NyvUcTqIo</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>transmitido pelo canal no YouTube do Legislativo Municipal</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/prestacao-de-contas-do-municipio-e-apresentada-em-audiencia-na-camara</t>
+        </is>
+      </c>
+      <c r="F2192" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2192" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.leg.br/sessoes-plenarias/audiencias-publicas-1/2022/poder-executivo/2o-quadrimestre-2022/apresentacao/at_download/file</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>www.toledo.pr.leg.br</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>informações</t>
+        </is>
+      </c>
+      <c r="E2193" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/prestacao-de-contas-do-municipio-e-apresentada-em-audiencia-na-camara</t>
+        </is>
+      </c>
+      <c r="F2193" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2193" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfOKGYW9VN_eFDLc6Z4wp6oq2ovdVX5o_59rOigKE9ECq6V4w/viewform</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>uma pesquisa com os usuários do transporte coletivo</t>
+        </is>
+      </c>
+      <c r="E2194" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/administracao-municipal-inicia-pesquisa-sobre-o-transporte-coletivo-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2194" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2194" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L4Iz0rKEr1w</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>apresentada na Câmara de Vereadores durante a audiência quadrimestral (referente aos meses de maio, junho, julho e agosto)</t>
+        </is>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/audiencia-quadrimestral-aponta-avancos-nos-servicos-de-saude-municipais</t>
+        </is>
+      </c>
+      <c r="F2195" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2195" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:14:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>https://www.qrfy.com/sXjj8CR</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>www.qrfy.com</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>este link</t>
+        </is>
+      </c>
+      <c r="E2196" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/procontoledo-promove-curso-de-educacao-financeira-para-consumidores</t>
+        </is>
+      </c>
+      <c r="F2196" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2196" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/Cis6sQmrH-7/?utm_source=ig_web_copy_link</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>Joca Martins</t>
+        </is>
+      </c>
+      <c r="E2197" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/fim-de-semana-tera-shows-com-grandes-nomes-do-tradicionalismo-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2197" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2197" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/Civt8JCpvJS/?utm_source=ig_web_copy_link</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>Quarteto Coração de Potro</t>
+        </is>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/fim-de-semana-tera-shows-com-grandes-nomes-do-tradicionalismo-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2198" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2198" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/Ci04WLVJkHC/?utm_source=ig_web_copy_link</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>Os Monarcas</t>
+        </is>
+      </c>
+      <c r="E2199" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/fim-de-semana-tera-shows-com-grandes-nomes-do-tradicionalismo-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2199" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2199" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/CiyHa7QpiY1/?utm_source=ig_web_copy_link</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>Os Serranos</t>
+        </is>
+      </c>
+      <c r="E2200" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/fim-de-semana-tera-shows-com-grandes-nomes-do-tradicionalismo-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2200" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2200" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YfcuD5i_u-U</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>solenidade transmitida pelo canal da Casa de Leis no YouTube</t>
+        </is>
+      </c>
+      <c r="E2201" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/vereadores-mirins-tomam-posse-na-camara-municipal-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2201" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2201" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfWdak9pO8zvALHS6C_5ixCm6Q6qqivUBihofdJSP_-FqWKEg/viewform</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>Currículo Top</t>
+        </is>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/brf-abre-162-vagas-e-realiza-entrevistas-no-sinetoledo-nesta-sexta-feira-23</t>
+        </is>
+      </c>
+      <c r="F2202" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2202" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>http://www.jogosdajuventude.pr.gov.br/modules/fase_final/uploads/2022_jojups_final_class_xadrez_.pdf</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>www.jogosdajuventude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>Os demais resultados podem ser acessados no site dos Jogos da Juventude do Paraná</t>
+        </is>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/primeira-etapa-do-jojups-apontou-campeoes-em-quatro-modalidades-e-semifinalistas-em-duas</t>
+        </is>
+      </c>
+      <c r="F2203" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2203" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>http://www.jogosdajuventude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>www.jogosdajuventude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>www.jogosdajuventude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/primeira-etapa-do-jojups-apontou-campeoes-em-quatro-modalidades-e-semifinalistas-em-duas</t>
+        </is>
+      </c>
+      <c r="F2204" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2204" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/519502801474714/posts/pfbid02344BK3irF2bBV2pyY42LdFnDWvXdqFBM27yaSGy9hHQ6sAzvSPUvkmUpuXKiuSoVl/?sfnsn=wiwspmo</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E2205" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/outros-200-outras-historias-willy-barth-esta-na-16a-primavera-dos-museus</t>
+        </is>
+      </c>
+      <c r="F2205" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2205" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vog0s9qNe2k</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="E2206" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/com-orcamento-total-de-r-8786-milhoes-toledo-apresenta-loa-de-2023</t>
+        </is>
+      </c>
+      <c r="F2206" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2206" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>https://abre.ai/e0Yn</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>abre.ai</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>formulário eletrônico</t>
+        </is>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/com-orcamento-total-de-r-8786-milhoes-toledo-apresenta-loa-de-2023</t>
+        </is>
+      </c>
+      <c r="F2207" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2207" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>http://www.jogosdajuventude.pr.gov.br/modules/fase_final/fase.php?fase=29&amp;cmbRegional=218&amp;TipoDoc=2</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>www.jogosdajuventude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>A programação completa está no site dos Jogos da Juventude do Paraná</t>
+        </is>
+      </c>
+      <c r="E2208" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/reuniao-com-equipes-marca-inicio-da-fase-final-dos-jojups-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2208" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2208" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/smed.toledo.pr.gov.br/smed/inicio?authuser=0</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>sites.google.com</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>A programação completa e os locais das palestras e oficinas podem ser acessados no site do evento</t>
+        </is>
+      </c>
+      <c r="E2209" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/smed-abre-inscricoes-para-vagas-remanescentes-do-compei</t>
+        </is>
+      </c>
+      <c r="F2209" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2209" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdctbhunOXWJpMKSJdrA3jhtEpAkv-sDXOckupdg5_E-AbmLA/viewform</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdctbhunOXWJpMKSJdrA3jhtEpAkv-sDXOckupdg5_E-AbmLA/viewform</t>
+        </is>
+      </c>
+      <c r="E2210" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/smed-abre-inscricoes-para-vagas-remanescentes-do-compei</t>
+        </is>
+      </c>
+      <c r="F2210" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2210" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:15:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/d/u/0/viewer?mid=1siRsnBTcEAsa2Zttl7DJc0N6muENHiG6&amp;ll=-24.73194598075408%2C-53.741408374172906&amp;z=15</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>Mapeamento Setorial das Políticas de Atendimento a Criança e Adolescente no Município de Toledo - PR</t>
+        </is>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/toledo-realiza-mapeamento-de-servicos-que-atendem-criancas-e-adolescentes</t>
+        </is>
+      </c>
+      <c r="F2211" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2211" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:16:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1V0sF9yaHHKWTbeJx9cyvW3nS_wOq0VGfQEKuhA76hAI/edit</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>Clique aqui para ver a programação e se inscrever</t>
+        </is>
+      </c>
+      <c r="E2212" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/parque-do-povo-sera-o-foco-das-acoes-de-plantio-durante-a-semana-da-arvore</t>
+        </is>
+      </c>
+      <c r="F2212" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2212" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:16:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1B5VhwailnvXsM28CMqwLJpAV_1nDQrBquUhrfRI9It0/edit</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>As inscrições para a oficina podem ser realizadas aqui</t>
+        </is>
+      </c>
+      <c r="E2213" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/parque-do-povo-sera-o-foco-das-acoes-de-plantio-durante-a-semana-da-arvore</t>
+        </is>
+      </c>
+      <c r="F2213" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2213" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:16:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>https://fb.watch/fpRzMpDY1I/</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>fb.watch</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>foi realizada mais uma live para anunciar melhorias para os trabalhadores da administração municipal</t>
+        </is>
+      </c>
+      <c r="E2214" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/cast-apresenta-avancos-para-os-servidores-conveniados-em-transmissao-ao-vivo</t>
+        </is>
+      </c>
+      <c r="F2214" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2214" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:16:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>http://www.sanepar.com.br/</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>www.sanepar.com.br</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>www.sanepar.com.br</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/utilidade-publica-queima-de-motor-afeta-o-abastecimento-em-bairros-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2215" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2215" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>http://www.ibge.gov.br</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>www.ibge.gov.br</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>www.ibge.gov.br</t>
+        </is>
+      </c>
+      <c r="E2216" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/apoio-da-populacao-e-fundamental-para-sucesso-do-censo-2022-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2216" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2216" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>https://www.saude.pr.gov.br/Endereco/Consorcio-Intermunicipal-de-Saude-Costa-Oeste-do-Parana-CISCOPAR</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>www.saude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>Consórcio Intermunicipal de Saúde Costa Oeste do Paraná</t>
+        </is>
+      </c>
+      <c r="E2217" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/consultores-da-camem-visitam-estruturas-de-saude-do-municipio-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2217" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2217" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>http://www.femipa.org.br/afiliados/hoesp-associacao-beneficente-de-saude-do-oeste-do-parana/</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>www.femipa.org.br</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>Associação Beneficente de Saúde do Oeste do Paraná</t>
+        </is>
+      </c>
+      <c r="E2218" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/consultores-da-camem-visitam-estruturas-de-saude-do-municipio-de-toledo</t>
+        </is>
+      </c>
+      <c r="F2218" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2218" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfwHfpSyIBojxLs_MV41kFT-2J5h5Z62eS9WItXsIzNpjvhAw/viewform</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>formulário eletrônico</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/desfile-civico-de-7-de-setembro-ja-tem-presenca-confirmada-de-142-delegacoes</t>
+        </is>
+      </c>
+      <c r="F2219" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2219" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>https://nam12.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.toledo.pr.gov.br%2F&amp;data=05%7C01%7C%7C0f2dfb1684404bbcfc0908da84470119%7C84df9e7fe9f640afb435aaaaaaaaaaaa%7C1%7C0%7C637967737778983107%7CUnknown%7CTWFpbGZsb3d8eyJWIjoiMC4wLjAwMDAiLCJQIjoiV2luMzIiLCJBTiI6Ik1haWwiLCJXVCI6Mn0%3D%7C3000%7C%7C%7C&amp;sdata=ZDRsq17ujjFhGTfgwwEF2dC46mb7RVwUXvHhrMU3MvI%3D&amp;reserved=0</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>nam12.safelinks.protection.outlook.com</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>www.toledo.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/jogos-dos-idosos-de-toledo-smel-define-datas-para-a-competicao</t>
+        </is>
+      </c>
+      <c r="F2220" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2220" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VbK2WBSxzhc</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>entrevista concedida ao programa “Provoca”</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/grandes-nomes-da-literatura-brasileira-vem-a-toledo-prestigiar-a-flit</t>
+        </is>
+      </c>
+      <c r="F2221" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2221" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/Poeta</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>poeta</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/grandes-nomes-da-literatura-brasileira-vem-a-toledo-prestigiar-a-flit</t>
+        </is>
+      </c>
+      <c r="F2222" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2222" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/Dramaturgo</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>dramaturgo</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/grandes-nomes-da-literatura-brasileira-vem-a-toledo-prestigiar-a-flit</t>
+        </is>
+      </c>
+      <c r="F2223" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2223" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/Portugueses</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>português</t>
+        </is>
+      </c>
+      <c r="E2224" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/grandes-nomes-da-literatura-brasileira-vem-a-toledo-prestigiar-a-flit</t>
+        </is>
+      </c>
+      <c r="F2224" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2224" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:17:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PrefeituraMunicipalToledo/videos/781006319985982</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>com transmissão ao vivo pelas redes sociais da Secretaria de Cultura</t>
+        </is>
+      </c>
+      <c r="E2225" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/secretaria-da-cultura-e-unioeste-anunciam-vencedores-e-lancam-6a-coletanea-do-concurso-paulo</t>
+        </is>
+      </c>
+      <c r="F2225" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2225" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>https://fb.watch/ePG6KZN1Bx/</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>fb.watch</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>anunciou por meio de uma transmissão ao vivo pelas redes sociais oficiais da Prefeitura de Toledo a empresa vencedora do processo licitatório para o vale alimentação dos servidores públicos municipais</t>
+        </is>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/administracao-municipal-anuncia-novo-vale-alimentacao-em-transmissao-ao-vivo</t>
+        </is>
+      </c>
+      <c r="F2226" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2226" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X_0nw0S03Uc</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>Canção 10 de Agosto</t>
+        </is>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/governo-municipal-prestigia-solenidade-do-168o-aniversario-da-pmpr</t>
+        </is>
+      </c>
+      <c r="F2227" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2227" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:18:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2015-2018/2017/lei/l13460.htm</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>Lei Federal 13.460/2017</t>
+        </is>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/servidores-municipais-que-operam-o-eouve-participam-de-treinamento</t>
+        </is>
+      </c>
+      <c r="F2228" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2228" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>http://www.emdur.com.br/licita%C3%A7%C3%A3o</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>www.emdur.com.br</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>www.emdur.com.br/licitação</t>
+        </is>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/emdur-realiza-no-proximo-dia-30-leilao-para-alienacao-de-bens-inserviveis</t>
+        </is>
+      </c>
+      <c r="F2229" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2229" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>https://emdur.com.br/licitacaoView/?id=488</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>emdur.com.br</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>Leilão 1/2022</t>
+        </is>
+      </c>
+      <c r="E2230" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/emdur-realiza-no-proximo-dia-30-leilao-para-alienacao-de-bens-inserviveis</t>
+        </is>
+      </c>
+      <c r="F2230" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2230" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>https://www.legislacao.pr.gov.br/legislacao/pesquisarAto.do?action=exibir&amp;codAto=227898&amp;indice=1&amp;totalRegistros=1&amp;dt=10.7.2021.0.28.28.962</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>www.legislacao.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>Lei Estadual 19.972/2019</t>
+        </is>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/integrantes-da-rede-de-protecao-participam-do-2o-seminario-mulheres-em-foco</t>
+        </is>
+      </c>
+      <c r="F2231" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2231" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:19:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2004-2006/2006/lei/l11340.htm</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>Lei Maria da Penha</t>
+        </is>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/integrantes-da-rede-de-protecao-participam-do-2o-seminario-mulheres-em-foco</t>
+        </is>
+      </c>
+      <c r="F2232" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2232" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:19:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CgPlw_7rt0M/</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>A campanha, no perfil oficial da Prefeitura de Toledo no Instagram, já tem quase mil curtidas e vários comentários</t>
+        </is>
+      </c>
+      <c r="E2233" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/vai-dar-adocao-acontece-neste-domingo</t>
+        </is>
+      </c>
+      <c r="F2233" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2233" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:19:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>https://www.legislacao.pr.gov.br/legislacao/pesquisarAto.do?action=exibir&amp;codAto=221885&amp;indice=1&amp;totalRegistros=1&amp;dt=22.6.2022.15.50.37.746</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>www.legislacao.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>Lei n° 19.873/2019</t>
+        </is>
+      </c>
+      <c r="E2234" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/dia-estadual-de-combate-ao-feminicidio-motiva-blitz-educativa-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2234" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2234" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>http://equiplano.toledo.pr.gov.br:7474/transparencia/contratos/verContrato?formulario.codEntidade=136&amp;formulario.exercicio=2021&amp;formulario.codFornecedor=11431266&amp;formulario.idContrato=22671&amp;formulario.tpAto=Contrato</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>equiplano.toledo.pr.gov.br:7474</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>Contrato nº 1.173/2021</t>
+        </is>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/prefeitura-de-toledo-rescinde-contrato-com-empresa-do-auxilio-alimentacao</t>
+        </is>
+      </c>
+      <c r="F2235" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2235" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:20:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>http://www.ruraltoledo.com.br</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>www.ruraltoledo.com.br</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>www.ruraltoledo.com.br</t>
+        </is>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/cursos-sobre-olericultura-e-turismo-rural-tem-apoio-da-agrodesenvolvimento</t>
+        </is>
+      </c>
+      <c r="F2236" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2236" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:20:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>https://forms.gle/W5RQGQQzxUQ4D5gf9</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>https://forms.gle/W5RQGQQzxUQ4D5gf9</t>
+        </is>
+      </c>
+      <c r="E2237" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/agencia-do-trabalhador-e-brf-disponibilizam-50-vagas-para-jovem-aprendiz</t>
+        </is>
+      </c>
+      <c r="F2237" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2237" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:20:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>https://forms.gle/sRcNR4Ng5ZCRtPWo8</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>via internet</t>
+        </is>
+      </c>
+      <c r="E2238" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/7o-toledo-em-danca-secretaria-da-cultura-prorroga-inscricoes-para-ate-317</t>
+        </is>
+      </c>
+      <c r="F2238" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2238" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3AFho69</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3AFho69</t>
+        </is>
+      </c>
+      <c r="E2239" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/toledo-sedia-nesta-quinta-feira-21-1o-forum-estrategico-de-empregabilidade</t>
+        </is>
+      </c>
+      <c r="F2239" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2239" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:20:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>https://www.cpb.org.br/noticia/detalhe/3408/presidente-do-cpb-e-governador-do-parana-assinam-convenio-de-promocao-da-educacao-paralimpica</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>www.cpb.org.br</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>parceria firmada entre governo estadual e Comitê Paralímpico Brasileiro (CPB)</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/frente-paranaense-da-educacao-paralimpica-e-apresentada-em-toledo</t>
+        </is>
+      </c>
+      <c r="F2240" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2240" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/watch/live/?ref=watch_permalink&amp;v=768895180907403</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>em uma transmissão ao vivo nesta quarta-feira (13)</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/servidores-municipais-vao-poder-usar-qualificacoes-ead-para-progredir-na-carreira</t>
+        </is>
+      </c>
+      <c r="F2241" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2241" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:21:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>http://www.cbsk.com.br/cms/social/relacao-de-projetos-cadastrados/1946</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>www.cbsk.com.br</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>site da Confederação Brasileira de Skate</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/noticia/escolinha-de-skate-de-toledo-e-reconhecida-pela-cbsk</t>
+        </is>
+      </c>
+      <c r="F2242" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2242" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:21:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1y_fWKauXonRx9iadTZmgOi8dalawttJ8?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr"/>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/portal/plano-municipal-de-conservacao-e-recuperacao-da-mata-atlantica/plano-municipal-de-conservacao</t>
+        </is>
+      </c>
+      <c r="F2243" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2243" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:39:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>http://www.iap.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>www.iap.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>www.iap.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>https://www.toledo.pr.gov.br/old/book/export/html/2945</t>
+        </is>
+      </c>
+      <c r="F2244" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2244" t="inlineStr">
+        <is>
+          <t>2026-08-24 02:42:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>https://equiplano.toledo.pr.gov.br:7443/rh</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>equiplano.toledo.pr.gov.br:7443</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>Acessar Portal do Holerite</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>https://remo.toledo.pr.gov.br/login</t>
+        </is>
+      </c>
+      <c r="F2245" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2245" t="inlineStr">
+        <is>
+          <t>2026-08-24 03:21:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdJRCny_KSXgHqGAv4pFSLV_my-u3rPpGVb6UBL7ee-RXz2-w/viewform?usp=pp_url</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2246" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2246" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>https://forms.gle/zgo8MXJjeRTBvHxv6</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2247" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2247" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hC7WvPMhc9ctvwYU9</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2248" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2248" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>https://forms.gle/XJbiFo9BrZ73LLv99</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2249" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2249" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>https://forms.gle/6Ji5EGfg6KYFHGEV9</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2250" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2250" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>https://forms.gle/wzNmCcb9TyoF8inLA</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2251" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2251" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>https://forms.gle/JhHULfsWzoQCtjQw7</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2252" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2252" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Q7JqF5888U9sngW88</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2253" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2253" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ZbHfM3oEtNSDniiS8</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2254" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2254" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>https://forms.gle/rdZU7ATD5VfzPpbD7</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2255" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2255" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>https://forms.gle/VLuEHMYV8eiYxzR48</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2256" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2256" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>https://forms.gle/BU2cSUiwVnaifvAZ8</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2257" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2257" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>https://forms.gle/CJ5zGqYfX26VA9tB7</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2258" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2258" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>https://forms.gle/EC4VNEBkcWkEyrRGA</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2259" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2259" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Kg6ob2vu6A5aU2Nz6</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2260" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2260" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>https://forms.gle/HWkJWZLhCrDstSc56</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2261" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2261" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>https://forms.gle/2dzvQkjU6qmfJJFV7</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2262" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2262" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>https://forms.gle/PJ1GB6YqHtTXcC2t9</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2263" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2263" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>https://forms.gle/v6LqoQgLaTceYobq9</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2264" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2264" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hr53EPagKfkvVuo76</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - MATUTINO</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2265" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2265" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>https://forms.gle/fiGqXJkdP1erbqbTA</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2266" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2266" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>https://forms.gle/9m7A4UthddxJgXPi6</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2267" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2267" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>https://forms.gle/M8SPACDDUSKraNAY9</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2268" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2268" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>https://forms.gle/foTpu7ooz12wKx3G6</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2269" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2269" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Uc5yeevesQdAoqPW7</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2270" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2270" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>https://forms.gle/8fCxA9StsKYGLcLN9</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2271" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2271" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>https://forms.gle/w6TUGqFxqPxoD71z7</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2272" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2272" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ddAsiZzojmLLSdGF6</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2273" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2273" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>https://forms.gle/E79SDWceRynB6Wye7</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2274" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2274" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>https://forms.gle/vS6t19pCctJTPhqx8</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2275" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2275" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>https://forms.gle/vr3bzSybsNNA9pcu9</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2276" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2276" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ZrjUxfGVXScGeLDZ6</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2277" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2277" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>https://forms.gle/cpXPXHJkK7MBw8p6A</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2278" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2278" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>https://forms.gle/vaEvU8sN2qg5ojst9</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2279" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2279" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>https://forms.gle/wxHG2mhet8MZPmZn8</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2280" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2280" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ZMa4ZDAZHeiNXF5m6</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2281" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2281" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Ctr4yrdHduWiafxA7</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2282" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2282" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hCMHVRFo6qkfcL9M8</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2283" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2283" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>https://forms.gle/cdf9FFbNHcWSK8S39</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>INSCRIÇÃO - VESPERTINO</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>http://www.smed.toledo.pr.gov.br/xviiisemanaeducacaoinfantil23</t>
+        </is>
+      </c>
+      <c r="F2284" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2284" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/17_7P49ncB1vjRnPZtsZK6SDnPIHS4mJZ?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI - REFERENCIAL CURRICULAR PARA O SISTEMA DE ENSINO DE TOLEDO/PR</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2285" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2285" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1iVvjUZ80JMuj1iTBlZP-7EyAjsgcVzxa/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI PARA ACESSAR OREGIMENTO INTERNO DA CONFERÊNCIA MUNICIPAL DA EDUCAÇÃO DO REFERENCIAL CURRICULAR PARA O SISTEMA MUNICIPAL DE ENSINO DE TOLEDO – EDUCAÇÃO INFANTIL E ENSINO FUNDAMENTAL ANOS INCIAIS</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2286" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2286" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>https://forms.gle/qzynJcHGeEbYvpgH7</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2287" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2287" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>https://forms.gle/uMBCnsEP1gZ63VEK7</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2288" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2288" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>https://forms.gle/WrSUaRvwgbwAod6J6</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2289" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2289" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ortcov52t6QJzsTV9</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2290" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2290" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>https://forms.gle/T7ga65NzzZrxtkD29</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2291" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2291" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>https://forms.gle/9ea7HcGfUb1Cuy8g8</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2292" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2292" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>https://forms.gle/t4sDY7dgcBnKVWCe9</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2293" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2293" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>https://forms.gle/4v17zLSWanjMd4zw5</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2294" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2294" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Pbsjqim9pmQju2DC6</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2295" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2295" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>https://forms.gle/v16yMXueRpKGoCWt6</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2296" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2296" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>https://forms.gle/5gBa5SFvJuuYcTaP9</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2297" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2297" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ccNbA9aP65segEKU9</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2298" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2298" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>https://forms.gle/qMXUVbfhFPnebi8D9</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2299" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2299" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>https://forms.gle/P9w8fkVCbEBVUAkU9</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2300" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2300" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>https://forms.gle/acCSPbwg5p7EtZao8</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>https://www.smed.toledo.pr.gov.br/conferenciamunicipaldaeducacao</t>
+        </is>
+      </c>
+      <c r="F2301" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2301" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=305s</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=305s</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=23</t>
+        </is>
+      </c>
+      <c r="F2302" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2302" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ptyn0LNd3AE</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ptyn0LNd3AE</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=22</t>
+        </is>
+      </c>
+      <c r="F2303" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2303" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=609s</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=609s</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=8</t>
+        </is>
+      </c>
+      <c r="F2304" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2304" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=551s</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=551s</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=7</t>
+        </is>
+      </c>
+      <c r="F2305" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2305" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=487s</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=487s</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=6</t>
+        </is>
+      </c>
+      <c r="F2306" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2306" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=34s</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=34s</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=5</t>
+        </is>
+      </c>
+      <c r="F2307" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2307" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=381s</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=381s</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=4</t>
+        </is>
+      </c>
+      <c r="F2308" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2308" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>toledo</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=84s</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=23jaOl5sgYI&amp;t=84s</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>https://chamados.toledo.pr.gov.br/front/helpdesk.faq.php?id=1</t>
+        </is>
+      </c>
+      <c r="F2309" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2309" t="inlineStr">
+        <is>
+          <t>2026-08-24 07:15:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
